--- a/wwwroot/temp/教師資料匯入_公版.xlsx
+++ b/wwwroot/temp/教師資料匯入_公版.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jay_liu\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IISWebSize\MT\wwwroot\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE10509-E61E-4D29-967C-7DA25A5A177D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CF8604-48DF-4D26-9FD3-DCA3E79D963C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1787,7 +1787,7 @@
       <formula1>"男, 女"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576" xr:uid="{33F23AB1-F80B-4A10-9935-AE7AA07FB966}">
-      <formula1>"停用, 啟用"</formula1>
+      <formula1>"啟用, 停用"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{05549CB6-DA67-4952-B65A-C58A9940885E}">
       <formula1>"博士, 碩士, 學士, 專科, 其它"</formula1>
